--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B9" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R9" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B10" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R10" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R13" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R14" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1925,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133364560</v>
+        <v>133367059</v>
       </c>
       <c r="B27" t="n">
-        <v>83315</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462293</v>
+        <v>462625</v>
       </c>
       <c r="R27" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133365574</v>
+        <v>133364560</v>
       </c>
       <c r="B28" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462401</v>
+        <v>462293</v>
       </c>
       <c r="R28" t="n">
-        <v>6845972</v>
+        <v>6845839</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,45 +3327,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133367059</v>
+        <v>133365574</v>
       </c>
       <c r="B29" t="n">
-        <v>80467</v>
+        <v>79091</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462625</v>
+        <v>462401</v>
       </c>
       <c r="R29" t="n">
-        <v>6846158</v>
+        <v>6845972</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B4" t="n">
-        <v>78999</v>
+        <v>79090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R4" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B5" t="n">
-        <v>79090</v>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R5" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B9" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R9" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B10" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R10" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B20" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R20" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R21" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2833,45 +2833,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B24" t="n">
-        <v>78340</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R24" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,54 +2939,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>78340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R25" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133367059</v>
+        <v>133364560</v>
       </c>
       <c r="B27" t="n">
-        <v>80467</v>
+        <v>83315</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462625</v>
+        <v>462293</v>
       </c>
       <c r="R27" t="n">
-        <v>6846158</v>
+        <v>6845839</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133364560</v>
+        <v>133367059</v>
       </c>
       <c r="B28" t="n">
-        <v>83315</v>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462293</v>
+        <v>462625</v>
       </c>
       <c r="R28" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B4" t="n">
-        <v>79090</v>
+        <v>78999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R4" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>79090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R5" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B9" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R9" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B10" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R10" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133369230</v>
+        <v>133366466</v>
       </c>
       <c r="B15" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,34 +1962,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462820</v>
+        <v>462447</v>
       </c>
       <c r="R15" t="n">
-        <v>6845358</v>
+        <v>6846185</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133366466</v>
+        <v>133369230</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,34 +2059,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462447</v>
+        <v>462820</v>
       </c>
       <c r="R16" t="n">
-        <v>6846185</v>
+        <v>6845358</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133364560</v>
+        <v>133365574</v>
       </c>
       <c r="B27" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462293</v>
+        <v>462401</v>
       </c>
       <c r="R27" t="n">
-        <v>6845839</v>
+        <v>6845972</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133365574</v>
+        <v>133364560</v>
       </c>
       <c r="B29" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462401</v>
+        <v>462293</v>
       </c>
       <c r="R29" t="n">
-        <v>6845972</v>
+        <v>6845839</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133369165</v>
+        <v>133363927</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>79365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462802</v>
+        <v>462410</v>
       </c>
       <c r="R2" t="n">
-        <v>6845364</v>
+        <v>6845795</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133363927</v>
+        <v>133369165</v>
       </c>
       <c r="B3" t="n">
-        <v>79365</v>
+        <v>79428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462410</v>
+        <v>462802</v>
       </c>
       <c r="R3" t="n">
-        <v>6845795</v>
+        <v>6845364</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B4" t="n">
-        <v>78999</v>
+        <v>79090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R4" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B5" t="n">
-        <v>79090</v>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R5" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B9" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R9" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B10" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R10" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R13" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1865,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R14" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2833,54 +2833,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>78340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R24" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2939,45 +2930,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B25" t="n">
-        <v>78340</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R25" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133365574</v>
+        <v>133367059</v>
       </c>
       <c r="B27" t="n">
-        <v>79091</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462401</v>
+        <v>462625</v>
       </c>
       <c r="R27" t="n">
-        <v>6845972</v>
+        <v>6846158</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133367059</v>
+        <v>133364560</v>
       </c>
       <c r="B28" t="n">
-        <v>80467</v>
+        <v>83315</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462625</v>
+        <v>462293</v>
       </c>
       <c r="R28" t="n">
-        <v>6846158</v>
+        <v>6845839</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133364560</v>
+        <v>133365574</v>
       </c>
       <c r="B29" t="n">
-        <v>83315</v>
+        <v>79091</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462293</v>
+        <v>462401</v>
       </c>
       <c r="R29" t="n">
-        <v>6845839</v>
+        <v>6845972</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B4" t="n">
-        <v>79090</v>
+        <v>78999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R4" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>79090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R5" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133363927</v>
+        <v>133369165</v>
       </c>
       <c r="B2" t="n">
-        <v>79365</v>
+        <v>79428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462410</v>
+        <v>462802</v>
       </c>
       <c r="R2" t="n">
-        <v>6845795</v>
+        <v>6845364</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133369165</v>
+        <v>133363927</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>79365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462802</v>
+        <v>462410</v>
       </c>
       <c r="R3" t="n">
-        <v>6845364</v>
+        <v>6845795</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R13" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R14" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1925,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133366466</v>
+        <v>133369230</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,34 +1962,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462447</v>
+        <v>462820</v>
       </c>
       <c r="R15" t="n">
-        <v>6846185</v>
+        <v>6845358</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133369230</v>
+        <v>133366466</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,34 +2059,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462820</v>
+        <v>462447</v>
       </c>
       <c r="R16" t="n">
-        <v>6845358</v>
+        <v>6846185</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R20" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B21" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R21" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133368581</v>
+        <v>133364801</v>
       </c>
       <c r="B7" t="n">
-        <v>78999</v>
+        <v>83315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462723</v>
+        <v>462274</v>
       </c>
       <c r="R7" t="n">
-        <v>6845475</v>
+        <v>6845845</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133364801</v>
+        <v>133368581</v>
       </c>
       <c r="B8" t="n">
-        <v>83315</v>
+        <v>78999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462274</v>
+        <v>462723</v>
       </c>
       <c r="R8" t="n">
-        <v>6845845</v>
+        <v>6845475</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133367059</v>
+        <v>133365574</v>
       </c>
       <c r="B27" t="n">
-        <v>80467</v>
+        <v>79091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462625</v>
+        <v>462401</v>
       </c>
       <c r="R27" t="n">
-        <v>6846158</v>
+        <v>6845972</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133364560</v>
+        <v>133367059</v>
       </c>
       <c r="B28" t="n">
-        <v>83315</v>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462293</v>
+        <v>462625</v>
       </c>
       <c r="R28" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133365574</v>
+        <v>133364560</v>
       </c>
       <c r="B29" t="n">
-        <v>79091</v>
+        <v>83315</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462401</v>
+        <v>462293</v>
       </c>
       <c r="R29" t="n">
-        <v>6845972</v>
+        <v>6845839</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133364801</v>
+        <v>133368581</v>
       </c>
       <c r="B7" t="n">
-        <v>83315</v>
+        <v>78999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462274</v>
+        <v>462723</v>
       </c>
       <c r="R7" t="n">
-        <v>6845845</v>
+        <v>6845475</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133368581</v>
+        <v>133364801</v>
       </c>
       <c r="B8" t="n">
-        <v>78999</v>
+        <v>83315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462723</v>
+        <v>462274</v>
       </c>
       <c r="R8" t="n">
-        <v>6845475</v>
+        <v>6845845</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -2833,45 +2833,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B24" t="n">
-        <v>78340</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R24" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,54 +2939,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>78340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R25" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133369165</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>79429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133363927</v>
       </c>
       <c r="B3" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B4" t="n">
-        <v>78999</v>
+        <v>79091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R4" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B5" t="n">
-        <v>79090</v>
+        <v>79000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R5" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1071,7 +1071,7 @@
         <v>133367713</v>
       </c>
       <c r="B6" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133368581</v>
+        <v>133364801</v>
       </c>
       <c r="B7" t="n">
-        <v>78999</v>
+        <v>83316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462723</v>
+        <v>462274</v>
       </c>
       <c r="R7" t="n">
-        <v>6845475</v>
+        <v>6845845</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133364801</v>
+        <v>133368581</v>
       </c>
       <c r="B8" t="n">
-        <v>83315</v>
+        <v>79000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462274</v>
+        <v>462723</v>
       </c>
       <c r="R8" t="n">
-        <v>6845845</v>
+        <v>6845475</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B9" t="n">
-        <v>83315</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R9" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B10" t="n">
-        <v>79091</v>
+        <v>83316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R10" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1565,7 +1565,7 @@
         <v>133365335</v>
       </c>
       <c r="B11" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>133365094</v>
       </c>
       <c r="B12" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>133366197</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133369230</v>
       </c>
       <c r="B15" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133366466</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>133366491</v>
       </c>
       <c r="B17" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>133363915</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>133363793</v>
       </c>
       <c r="B19" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B20" t="n">
-        <v>79412</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R20" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R21" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2739,7 +2739,7 @@
         <v>133366378</v>
       </c>
       <c r="B23" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>78341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R24" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2939,45 +2930,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B25" t="n">
-        <v>78340</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R25" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3039,7 +3039,7 @@
         <v>133366090</v>
       </c>
       <c r="B26" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133365574</v>
+        <v>133364560</v>
       </c>
       <c r="B27" t="n">
-        <v>79091</v>
+        <v>83316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462401</v>
+        <v>462293</v>
       </c>
       <c r="R27" t="n">
-        <v>6845972</v>
+        <v>6845839</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3233,7 +3233,7 @@
         <v>133367059</v>
       </c>
       <c r="B28" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133364560</v>
+        <v>133365574</v>
       </c>
       <c r="B29" t="n">
-        <v>83315</v>
+        <v>79092</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462293</v>
+        <v>462401</v>
       </c>
       <c r="R29" t="n">
-        <v>6845839</v>
+        <v>6845972</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>79413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R20" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B21" t="n">
-        <v>79413</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R21" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2833,45 +2833,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B24" t="n">
-        <v>78341</v>
+        <v>57145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R24" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,54 +2939,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>78341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R25" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B20" t="n">
-        <v>79413</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R20" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R21" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B24" t="n">
-        <v>57145</v>
+        <v>78341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R24" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2939,45 +2930,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B25" t="n">
-        <v>78341</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R25" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1071,7 +1071,7 @@
         <v>133367713</v>
       </c>
       <c r="B6" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>133364801</v>
       </c>
       <c r="B7" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B9" t="n">
-        <v>79092</v>
+        <v>83319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R9" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B10" t="n">
-        <v>83316</v>
+        <v>79092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R10" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1662,7 +1662,7 @@
         <v>133365094</v>
       </c>
       <c r="B12" t="n">
-        <v>91940</v>
+        <v>91948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>133366491</v>
       </c>
       <c r="B17" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>79413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R20" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B21" t="n">
-        <v>79413</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R21" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2739,7 +2739,7 @@
         <v>133366378</v>
       </c>
       <c r="B23" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133364560</v>
+        <v>133367059</v>
       </c>
       <c r="B27" t="n">
-        <v>83316</v>
+        <v>80468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462293</v>
+        <v>462625</v>
       </c>
       <c r="R27" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133367059</v>
+        <v>133364560</v>
       </c>
       <c r="B28" t="n">
-        <v>80468</v>
+        <v>83319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462625</v>
+        <v>462293</v>
       </c>
       <c r="R28" t="n">
-        <v>6846158</v>
+        <v>6845839</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B4" t="n">
-        <v>79091</v>
+        <v>79000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R4" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B5" t="n">
-        <v>79000</v>
+        <v>79091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R5" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R13" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1865,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R14" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R13" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R14" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1925,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R13" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1865,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R14" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B9" t="n">
-        <v>83319</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R9" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B10" t="n">
-        <v>79092</v>
+        <v>83319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R10" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133369165</v>
       </c>
       <c r="B2" t="n">
-        <v>79429</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133363927</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133368738</v>
+        <v>133363794</v>
       </c>
       <c r="B4" t="n">
-        <v>79000</v>
+        <v>79105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462637</v>
+        <v>462504</v>
       </c>
       <c r="R4" t="n">
-        <v>6845395</v>
+        <v>6845804</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B5" t="n">
-        <v>79091</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R5" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1071,7 +1071,7 @@
         <v>133367713</v>
       </c>
       <c r="B6" t="n">
-        <v>93216</v>
+        <v>93244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>133364801</v>
       </c>
       <c r="B7" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>133368581</v>
       </c>
       <c r="B8" t="n">
-        <v>79000</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133366888</v>
+        <v>133365248</v>
       </c>
       <c r="B9" t="n">
-        <v>79092</v>
+        <v>83333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462581</v>
+        <v>462331</v>
       </c>
       <c r="R9" t="n">
-        <v>6846134</v>
+        <v>6845963</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133365248</v>
+        <v>133366888</v>
       </c>
       <c r="B10" t="n">
-        <v>83319</v>
+        <v>79106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462331</v>
+        <v>462581</v>
       </c>
       <c r="R10" t="n">
-        <v>6845963</v>
+        <v>6846134</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1565,7 +1565,7 @@
         <v>133365335</v>
       </c>
       <c r="B11" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>133365094</v>
       </c>
       <c r="B12" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R13" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1865,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R14" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1954,7 +1954,7 @@
         <v>133369230</v>
       </c>
       <c r="B15" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133366466</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>133366491</v>
       </c>
       <c r="B17" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>133363915</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>133363793</v>
       </c>
       <c r="B19" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133366236</v>
+        <v>133364887</v>
       </c>
       <c r="B20" t="n">
-        <v>79413</v>
+        <v>79348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,34 +2447,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462415</v>
+        <v>462287</v>
       </c>
       <c r="R20" t="n">
-        <v>6846174</v>
+        <v>6845853</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133364887</v>
+        <v>133366236</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2544,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462287</v>
+        <v>462415</v>
       </c>
       <c r="R21" t="n">
-        <v>6845853</v>
+        <v>6846174</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2633,7 +2633,7 @@
         <v>133364485</v>
       </c>
       <c r="B22" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>133366378</v>
       </c>
       <c r="B23" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>133369315</v>
       </c>
       <c r="B24" t="n">
-        <v>78341</v>
+        <v>78352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>133368661</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>133366090</v>
       </c>
       <c r="B26" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>133367059</v>
       </c>
       <c r="B27" t="n">
-        <v>80468</v>
+        <v>80482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>133364560</v>
       </c>
       <c r="B28" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>133365574</v>
       </c>
       <c r="B29" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133367059</v>
+        <v>133365574</v>
       </c>
       <c r="B27" t="n">
-        <v>80482</v>
+        <v>79106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462625</v>
+        <v>462401</v>
       </c>
       <c r="R27" t="n">
-        <v>6846158</v>
+        <v>6845972</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133364560</v>
+        <v>133367059</v>
       </c>
       <c r="B28" t="n">
-        <v>83333</v>
+        <v>80482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462293</v>
+        <v>462625</v>
       </c>
       <c r="R28" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133365574</v>
+        <v>133364560</v>
       </c>
       <c r="B29" t="n">
-        <v>79106</v>
+        <v>83333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462401</v>
+        <v>462293</v>
       </c>
       <c r="R29" t="n">
-        <v>6845972</v>
+        <v>6845839</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133369165</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133363927</v>
       </c>
       <c r="B3" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133363794</v>
       </c>
       <c r="B4" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>133368738</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>133367713</v>
       </c>
       <c r="B6" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>133364801</v>
       </c>
       <c r="B7" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>133368581</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>133365248</v>
       </c>
       <c r="B9" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>133366888</v>
       </c>
       <c r="B10" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>133365335</v>
       </c>
       <c r="B11" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>133365094</v>
       </c>
       <c r="B12" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>133364658</v>
       </c>
       <c r="B13" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>133366197</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133369230</v>
       </c>
       <c r="B15" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133366466</v>
       </c>
       <c r="B16" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>133366491</v>
       </c>
       <c r="B17" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>133363915</v>
       </c>
       <c r="B18" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>133363793</v>
       </c>
       <c r="B19" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>133364887</v>
       </c>
       <c r="B20" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>133366236</v>
       </c>
       <c r="B21" t="n">
-        <v>79427</v>
+        <v>79437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>133364485</v>
       </c>
       <c r="B22" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>133366378</v>
       </c>
       <c r="B23" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>133369315</v>
       </c>
       <c r="B24" t="n">
-        <v>78352</v>
+        <v>78362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>133368661</v>
       </c>
       <c r="B25" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>133366090</v>
       </c>
       <c r="B26" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133365574</v>
+        <v>133367059</v>
       </c>
       <c r="B27" t="n">
-        <v>79106</v>
+        <v>80478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462401</v>
+        <v>462625</v>
       </c>
       <c r="R27" t="n">
-        <v>6845972</v>
+        <v>6846158</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133367059</v>
+        <v>133364560</v>
       </c>
       <c r="B28" t="n">
-        <v>80482</v>
+        <v>83343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462625</v>
+        <v>462293</v>
       </c>
       <c r="R28" t="n">
-        <v>6846158</v>
+        <v>6845839</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133364560</v>
+        <v>133365574</v>
       </c>
       <c r="B29" t="n">
-        <v>83333</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462293</v>
+        <v>462401</v>
       </c>
       <c r="R29" t="n">
-        <v>6845839</v>
+        <v>6845972</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133369165</v>
+        <v>133363927</v>
       </c>
       <c r="B2" t="n">
-        <v>79453</v>
+        <v>79390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462802</v>
+        <v>462410</v>
       </c>
       <c r="R2" t="n">
-        <v>6845364</v>
+        <v>6845795</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133363927</v>
+        <v>133369165</v>
       </c>
       <c r="B3" t="n">
-        <v>79390</v>
+        <v>79453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462410</v>
+        <v>462802</v>
       </c>
       <c r="R3" t="n">
-        <v>6845795</v>
+        <v>6845364</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133364801</v>
+        <v>133368581</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>79024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462274</v>
+        <v>462723</v>
       </c>
       <c r="R7" t="n">
-        <v>6845845</v>
+        <v>6845475</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133368581</v>
+        <v>133364801</v>
       </c>
       <c r="B8" t="n">
-        <v>79024</v>
+        <v>83343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462723</v>
+        <v>462274</v>
       </c>
       <c r="R8" t="n">
-        <v>6845475</v>
+        <v>6845845</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R13" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R14" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1925,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2833,45 +2833,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B24" t="n">
-        <v>78362</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R24" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,54 +2939,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>78362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R25" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133367059</v>
+        <v>133365574</v>
       </c>
       <c r="B27" t="n">
-        <v>80478</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462625</v>
+        <v>462401</v>
       </c>
       <c r="R27" t="n">
-        <v>6846158</v>
+        <v>6845972</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133364560</v>
+        <v>133367059</v>
       </c>
       <c r="B28" t="n">
-        <v>83343</v>
+        <v>80478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462293</v>
+        <v>462625</v>
       </c>
       <c r="R28" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133365574</v>
+        <v>133364560</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>83343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462401</v>
+        <v>462293</v>
       </c>
       <c r="R29" t="n">
-        <v>6845972</v>
+        <v>6845839</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133363927</v>
+        <v>133369165</v>
       </c>
       <c r="B2" t="n">
-        <v>79390</v>
+        <v>79453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462410</v>
+        <v>462802</v>
       </c>
       <c r="R2" t="n">
-        <v>6845795</v>
+        <v>6845364</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133369165</v>
+        <v>133363927</v>
       </c>
       <c r="B3" t="n">
-        <v>79453</v>
+        <v>79390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462802</v>
+        <v>462410</v>
       </c>
       <c r="R3" t="n">
-        <v>6845364</v>
+        <v>6845795</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133368581</v>
+        <v>133364801</v>
       </c>
       <c r="B7" t="n">
-        <v>79024</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462723</v>
+        <v>462274</v>
       </c>
       <c r="R7" t="n">
-        <v>6845475</v>
+        <v>6845845</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133364801</v>
+        <v>133368581</v>
       </c>
       <c r="B8" t="n">
-        <v>83343</v>
+        <v>79024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462274</v>
+        <v>462723</v>
       </c>
       <c r="R8" t="n">
-        <v>6845845</v>
+        <v>6845475</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133366197</v>
+        <v>133364658</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462438</v>
+        <v>462279</v>
       </c>
       <c r="R13" t="n">
-        <v>6846159</v>
+        <v>6845862</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1849,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133364658</v>
+        <v>133366197</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1865,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462279</v>
+        <v>462438</v>
       </c>
       <c r="R14" t="n">
-        <v>6845862</v>
+        <v>6846159</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1920,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2833,54 +2833,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B24" t="n">
-        <v>57162</v>
+        <v>78362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R24" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2939,45 +2930,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133369315</v>
+        <v>133368661</v>
       </c>
       <c r="B25" t="n">
-        <v>78362</v>
+        <v>57162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462807</v>
+        <v>462658</v>
       </c>
       <c r="R25" t="n">
-        <v>6845387</v>
+        <v>6845409</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3133,45 +3133,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133365574</v>
+        <v>133367059</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>80478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462401</v>
+        <v>462625</v>
       </c>
       <c r="R27" t="n">
-        <v>6845972</v>
+        <v>6846158</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3230,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133367059</v>
+        <v>133364560</v>
       </c>
       <c r="B28" t="n">
-        <v>80478</v>
+        <v>83343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462625</v>
+        <v>462293</v>
       </c>
       <c r="R28" t="n">
-        <v>6846158</v>
+        <v>6845839</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133364560</v>
+        <v>133365574</v>
       </c>
       <c r="B29" t="n">
-        <v>83343</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462293</v>
+        <v>462401</v>
       </c>
       <c r="R29" t="n">
-        <v>6845839</v>
+        <v>6845972</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133369165</v>
+        <v>133363927</v>
       </c>
       <c r="B2" t="n">
-        <v>79453</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>967</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462802</v>
+        <v>462410</v>
       </c>
       <c r="R2" t="n">
-        <v>6845364</v>
+        <v>6845795</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133363927</v>
+        <v>133368581</v>
       </c>
       <c r="B3" t="n">
-        <v>79390</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462410</v>
+        <v>462723</v>
       </c>
       <c r="R3" t="n">
-        <v>6845795</v>
+        <v>6845475</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133363794</v>
+        <v>133368738</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462504</v>
+        <v>462637</v>
       </c>
       <c r="R4" t="n">
-        <v>6845804</v>
+        <v>6845395</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133368738</v>
+        <v>133366236</v>
       </c>
       <c r="B5" t="n">
-        <v>79024</v>
+        <v>79452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462637</v>
+        <v>462415</v>
       </c>
       <c r="R5" t="n">
-        <v>6845395</v>
+        <v>6846174</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1068,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133367713</v>
+        <v>133369165</v>
       </c>
       <c r="B6" t="n">
-        <v>93254</v>
+        <v>79468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462563</v>
+        <v>462802</v>
       </c>
       <c r="R6" t="n">
-        <v>6845915</v>
+        <v>6845364</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1148,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan 18164-2026.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133364801</v>
+        <v>133367713</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,34 +1176,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462274</v>
+        <v>462563</v>
       </c>
       <c r="R7" t="n">
-        <v>6845845</v>
+        <v>6845915</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133368581</v>
+        <v>133363915</v>
       </c>
       <c r="B8" t="n">
-        <v>79024</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462723</v>
+        <v>462419</v>
       </c>
       <c r="R8" t="n">
-        <v>6845475</v>
+        <v>6845805</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1368,32 +1368,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133365248</v>
+        <v>133364887</v>
       </c>
       <c r="B9" t="n">
-        <v>83343</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462331</v>
+        <v>462287</v>
       </c>
       <c r="R9" t="n">
-        <v>6845963</v>
+        <v>6845853</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1465,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133366888</v>
+        <v>133366197</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462581</v>
+        <v>462438</v>
       </c>
       <c r="R10" t="n">
-        <v>6846134</v>
+        <v>6846159</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1562,45 +1562,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133365335</v>
+        <v>133366466</v>
       </c>
       <c r="B11" t="n">
-        <v>79115</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462364</v>
+        <v>462447</v>
       </c>
       <c r="R11" t="n">
-        <v>6845946</v>
+        <v>6846185</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133365094</v>
+        <v>133364560</v>
       </c>
       <c r="B12" t="n">
-        <v>91977</v>
+        <v>83358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,19 +1670,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1690,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462315</v>
+        <v>462293</v>
       </c>
       <c r="R12" t="n">
-        <v>6845919</v>
+        <v>6845839</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1752,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133364658</v>
+        <v>133364801</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1767,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1791,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462279</v>
+        <v>462274</v>
       </c>
       <c r="R13" t="n">
-        <v>6845862</v>
+        <v>6845845</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1823,11 +1827,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133366197</v>
+        <v>133365248</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>83358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1864,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462438</v>
+        <v>462331</v>
       </c>
       <c r="R14" t="n">
-        <v>6846159</v>
+        <v>6845963</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1951,10 +1950,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133369230</v>
+        <v>133366378</v>
       </c>
       <c r="B15" t="n">
-        <v>79977</v>
+        <v>83358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,34 +1961,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462820</v>
+        <v>462438</v>
       </c>
       <c r="R15" t="n">
-        <v>6845358</v>
+        <v>6846188</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2048,10 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133366466</v>
+        <v>133366491</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>83358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2058,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462447</v>
+        <v>462465</v>
       </c>
       <c r="R16" t="n">
-        <v>6846185</v>
+        <v>6846196</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2145,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133366491</v>
+        <v>133363794</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>79130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,34 +2155,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462465</v>
+        <v>462504</v>
       </c>
       <c r="R17" t="n">
-        <v>6846196</v>
+        <v>6845804</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2242,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133363915</v>
+        <v>133365335</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>79130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462419</v>
+        <v>462364</v>
       </c>
       <c r="R18" t="n">
-        <v>6845805</v>
+        <v>6845946</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2342,7 +2341,7 @@
         <v>133363793</v>
       </c>
       <c r="B19" t="n">
-        <v>79977</v>
+        <v>79992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133364887</v>
+        <v>133369230</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>79992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>462287</v>
+        <v>462820</v>
       </c>
       <c r="R20" t="n">
-        <v>6845853</v>
+        <v>6845358</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2533,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133366236</v>
+        <v>133370870</v>
       </c>
       <c r="B21" t="n">
-        <v>79437</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,34 +2543,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462415</v>
+        <v>462905</v>
       </c>
       <c r="R21" t="n">
-        <v>6846174</v>
+        <v>6845883</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2630,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133364485</v>
+        <v>133367059</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>80493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,43 +2640,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462285</v>
+        <v>462625</v>
       </c>
       <c r="R22" t="n">
-        <v>6845839</v>
+        <v>6846158</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,45 +2726,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133366378</v>
+        <v>133370884</v>
       </c>
       <c r="B23" t="n">
-        <v>83343</v>
+        <v>80493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462438</v>
+        <v>462905</v>
       </c>
       <c r="R23" t="n">
-        <v>6846188</v>
+        <v>6845883</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133369315</v>
+        <v>133366692</v>
       </c>
       <c r="B24" t="n">
-        <v>78362</v>
+        <v>78377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2864,14 +2854,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462807</v>
+        <v>462536</v>
       </c>
       <c r="R24" t="n">
-        <v>6845387</v>
+        <v>6846059</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,54 +2920,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133368661</v>
+        <v>133369315</v>
       </c>
       <c r="B25" t="n">
-        <v>57162</v>
+        <v>78377</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>462658</v>
+        <v>462807</v>
       </c>
       <c r="R25" t="n">
-        <v>6845409</v>
+        <v>6845387</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3036,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133366090</v>
+        <v>133364658</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3047,37 +3028,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>462451</v>
+        <v>462279</v>
       </c>
       <c r="R26" t="n">
-        <v>6846089</v>
+        <v>6845862</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3107,6 +3088,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3133,10 +3119,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133367059</v>
+        <v>133364485</v>
       </c>
       <c r="B27" t="n">
-        <v>80478</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3144,34 +3130,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gönan, Gönan, Hjd</t>
+          <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462625</v>
+        <v>462285</v>
       </c>
       <c r="R27" t="n">
-        <v>6846158</v>
+        <v>6845839</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3230,45 +3225,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133364560</v>
+        <v>133366722</v>
       </c>
       <c r="B28" t="n">
-        <v>83343</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gönhållan, Gönhållan, Hjd</t>
+          <t>Gönan, Gönan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462293</v>
+        <v>462548</v>
       </c>
       <c r="R28" t="n">
-        <v>6845839</v>
+        <v>6846080</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3327,45 +3331,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133365574</v>
+        <v>133368661</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gönhållan, Gönhållan, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>462401</v>
+        <v>462658</v>
       </c>
       <c r="R29" t="n">
-        <v>6845972</v>
+        <v>6845409</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3421,6 +3434,703 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133370994</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gönhållan, Gönhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>462938</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6845865</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133366937</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gönan, Gönan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>462602</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6846123</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133365574</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gönhållan, Gönhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>462401</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6845972</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133366090</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gönan, Gönan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>462451</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6846089</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133366888</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gönan, Gönan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>462581</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6846134</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133367096</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gönan, Gönan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>462635</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6846179</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133370325</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gönhållan, Gönhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>462763</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6845879</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18164-2026 artfynd.xlsx
+++ b/artfynd/A 18164-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133368738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369165</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369230</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369315</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133368661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133363927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133368581</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366236</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133367713</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133363915</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133364887</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366197</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366466</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,6 +2123,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133364560</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133364801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133365248</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2344,6 +2429,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366378</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2441,6 +2531,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366491</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133363794</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2635,6 +2735,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133365335</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2732,6 +2837,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133363793</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2829,6 +2939,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133370870</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133367059</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3023,6 +3143,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133370884</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3120,6 +3245,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366692</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3222,6 +3352,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133364658</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3328,6 +3463,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133364485</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3434,6 +3574,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366722</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3540,6 +3685,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133370994</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3646,6 +3796,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366937</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3743,6 +3898,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133365574</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3840,6 +4000,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366090</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3937,6 +4102,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133366888</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4034,6 +4204,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133367096</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4131,8 +4306,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133370325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>